--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_repetition_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_repetition_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock?</t>
+          <t>What iis the locatiion off Eibenstock?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock? Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany. It is</t>
+          <t>What iis the locatiion off Eibenstock? Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin. Places nearby are Oberwies</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock?</t>
+          <t>What iis the locatiion off Eibenstock?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock? Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany. It is</t>
+          <t>What iis the locatiion off Eibenstock? Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin. Places nearby are Oberwies</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock?</t>
+          <t>What iis the locatiion off Eibenstock?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock? Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany. It is</t>
+          <t>What iis the locatiion off Eibenstock? Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin. Places nearby are Oberwies</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -627,7 +627,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock?</t>
+          <t>What iis the locatiion off Eibenstock?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock? Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany. It is</t>
+          <t>What iis the locatiion off Eibenstock? Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin. Places nearby are Oberwies</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock?</t>
+          <t>What iis the locatiion off Eibenstock?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WWhat is the loocation oof Eibenstock? Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany. It is</t>
+          <t>What iis the locatiion off Eibenstock? Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin. Places nearby are Oberwies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is a town in the district of Zwickau in the Free State of Saxony, Germany</t>
+          <t>Answer: Eibenstock is located in Germany (Sachsen) and time zone Europe/Berlin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool?</t>
+          <t>Whaat is the locationn of Simcoe Compositte School?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool? Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Whaat is the locationn of Simcoe Compositte School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 1.0), ('0', 1.0), (' Sim', 0.5), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 0.5), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool?</t>
+          <t>Whaat is the locationn of Simcoe Compositte School?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -797,29 +797,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool? Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Whaat is the locationn of Simcoe Compositte School? Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9460576772689819</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 1.0), ('0', 1.0), (' Sim', 0.5), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' St', 0.5), (',', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool?</t>
+          <t>Whaat is the locationn of Simcoe Compositte School?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool? Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Whaat is the locationn of Simcoe Compositte School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -867,7 +867,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 1.0), ('0', 1.0), (' Sim', 0.5), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 0.5), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool?</t>
+          <t>Whaat is the locationn of Simcoe Compositte School?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -893,29 +893,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool? Answer: Simcoe Composite School is located at 1000 2nd Ave. Simcoe, ON N3Y 4K</t>
+          <t>Whaat is the locationn of Simcoe Compositte School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1000 2nd Ave. Simcoe, ON N3Y 4K</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9460576772689819</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 1.0), ('0', 1.0), (' ', 0.5), ('2', 0.5), ('nd', 1.0), (' Ave', 1.0), ('.', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('K', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 0.5), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -928,7 +928,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool?</t>
+          <t>Whaat is the locationn of Simcoe Compositte School?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>What is the locationn of Simccoe Composite SSchool? Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Whaat is the locationn of Simcoe Compositte School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1000 Simcoe Street, Simcoe, Ontario N3Y 4H3</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3,</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -963,7 +963,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 1.0), ('0', 1.0), (' Sim', 0.5), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 0.5), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Whaat iss the location of Vrienden van het Platteland??</t>
+          <t>What is tthe location of Vriendenn van hett Platteland?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -989,33 +989,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whaat iss the location of Vrienden van het Platteland?? Answer: Vrienden van het Platteland is located in the Netherlands. The address of Vrienden van het Platteland is </t>
+          <t>What is tthe location of Vriendenn van hett Platteland? Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is not associated with Vriend</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
+          <t>Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is not associated with Vriend</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' The', 1.0), (' EU', 1.0), ('t', 1.0), ('ender', 1.0), (' notice', 1.0), (' has', 1.0), (' been', 1.0), (' updated', 1.0), ('.\n', 1.0), ('The', 1.0), (' fund', 1.0), (' has', 1.0), (' not', 1.0), (' updated', 1.0), (' their', 1.0), (' details', 1.0), ('!', 1.0), (' This', 1.0), (' website', 1.0), (' is', 1.0), (' not', 0.5), (' associated', 1.0), (' with', 1.0), (' V', 1.0), ('riend', 1.0)]</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1024,7 +1026,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Whaat iss the location of Vrienden van het Platteland??</t>
+          <t>What is tthe location of Vriendenn van hett Platteland?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1037,33 +1039,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whaat iss the location of Vrienden van het Platteland?? Answer: Vrienden van het Platteland is located in the Netherlands. The address of Vrienden van het Platteland is </t>
+          <t>What is tthe location of Vriendenn van hett Platteland? Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is updated by individual users.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
+          <t>Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is updated by individual users.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' The', 1.0), (' EU', 1.0), ('t', 1.0), ('ender', 1.0), (' notice', 1.0), (' has', 1.0), (' been', 1.0), (' updated', 1.0), ('.\n', 1.0), ('The', 1.0), (' fund', 1.0), (' has', 1.0), (' not', 1.0), (' updated', 1.0), (' their', 1.0), (' details', 1.0), ('!', 1.0), (' This', 1.0), (' website', 1.0), (' is', 1.0), (' updated', 0.5), (' by', 1.0), (' individual', 1.0), (' users', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Whaat iss the location of Vrienden van het Platteland??</t>
+          <t>What is tthe location of Vriendenn van hett Platteland?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1085,33 +1089,35 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whaat iss the location of Vrienden van het Platteland?? Answer: Vrienden van het Platteland is located in the Netherlands. The address of Vrienden van het Platteland is </t>
+          <t>What is tthe location of Vriendenn van hett Platteland? Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is not associated with Vriend</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
+          <t>Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is not associated with Vriend</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' The', 1.0), (' EU', 1.0), ('t', 1.0), ('ender', 1.0), (' notice', 1.0), (' has', 1.0), (' been', 1.0), (' updated', 1.0), ('.\n', 1.0), ('The', 1.0), (' fund', 1.0), (' has', 1.0), (' not', 1.0), (' updated', 1.0), (' their', 1.0), (' details', 1.0), ('!', 1.0), (' This', 1.0), (' website', 1.0), (' is', 1.0), (' not', 0.5), (' associated', 1.0), (' with', 1.0), (' V', 1.0), ('riend', 1.0)]</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1120,7 +1126,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Whaat iss the location of Vrienden van het Platteland??</t>
+          <t>What is tthe location of Vriendenn van hett Platteland?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1133,33 +1139,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whaat iss the location of Vrienden van het Platteland?? Answer: Vrienden van het Platteland is located in the Netherlands. The address of Vrienden van het Platteland is </t>
+          <t>What is tthe location of Vriendenn van hett Platteland? Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is updated by individual users.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
+          <t>Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is updated by individual users.</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' The', 1.0), (' EU', 1.0), ('t', 1.0), ('ender', 1.0), (' notice', 1.0), (' has', 1.0), (' been', 1.0), (' updated', 1.0), ('.\n', 1.0), ('The', 1.0), (' fund', 1.0), (' has', 1.0), (' not', 1.0), (' updated', 1.0), (' their', 1.0), (' details', 1.0), ('!', 1.0), (' This', 1.0), (' website', 1.0), (' is', 1.0), (' updated', 0.5), (' by', 1.0), (' individual', 1.0), (' users', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Whaat iss the location of Vrienden van het Platteland??</t>
+          <t>What is tthe location of Vriendenn van hett Platteland?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1181,33 +1189,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whaat iss the location of Vrienden van het Platteland?? Answer: Vrienden van het Platteland is located in the Netherlands. The address of Vrienden van het Platteland is </t>
+          <t>What is tthe location of Vriendenn van hett Platteland? Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is not associated with Vriend</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the Netherlands</t>
+          <t>Answer: The EUtender notice has been updated.
+The fund has not updated their details! This website is not associated with Vriend</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' The', 1.0), (' EU', 1.0), ('t', 1.0), ('ender', 1.0), (' notice', 1.0), (' has', 1.0), (' been', 1.0), (' updated', 1.0), ('.\n', 1.0), ('The', 1.0), (' fund', 1.0), (' has', 1.0), (' not', 1.0), (' updated', 1.0), (' their', 1.0), (' details', 1.0), ('!', 1.0), (' This', 1.0), (' website', 1.0), (' is', 1.0), (' not', 0.5), (' associated', 1.0), (' with', 1.0), (' V', 1.0), ('riend', 1.0)]</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1216,7 +1226,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer?</t>
+          <t>Whatt iss the llocation of Cunter?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1229,31 +1239,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer? Answer: Cunteer is located in the state of, in the.
-Where is Cunteer located? Answer: Cunteer is located in</t>
+          <t>Whatt iss the llocation of Cunter? Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Answer: Cunteer is located in the state of, in the.
-Where is Cunteer located? Answer: Cunteer is located in</t>
+          <t>Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.3754358887672424</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9615711569786072</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.547322154045105</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), ('.\n', 1.0), ('Where', 1.0), (' is', 1.0), (' C', 1.0), ('unteer', 1.0), (' located', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (' which', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Southern', 0.483), (' Australia', 0.7773), (' region', 1.0), (' of', 1.0), (' Australia', 1.0), ('.', 1.0), (' The', 1.0), (' latitude', 1.0), (' of', 1.0), (' C', 1.0), ('unter', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1266,7 +1274,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer?</t>
+          <t>Whatt iss the llocation of Cunter?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1279,31 +1287,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer? Answer: Cunteer is located in the state of, in the.
-Where is Cunteer located? Answer: Cunteer is located in</t>
+          <t>Whatt iss the llocation of Cunter? Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Answer: Cunteer is located in the state of, in the.
-Where is Cunteer located? Answer: Cunteer is located in</t>
+          <t>Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.3754358887672424</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9615711569786072</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.547322154045105</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), ('.\n', 1.0), ('Where', 1.0), (' is', 1.0), (' C', 1.0), ('unteer', 1.0), (' located', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (' which', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Southern', 0.483), (' Australia', 0.7773), (' region', 1.0), (' of', 1.0), (' Australia', 1.0), ('.', 1.0), (' The', 1.0), (' latitude', 1.0), (' of', 1.0), (' C', 1.0), ('unter', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1316,7 +1322,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer?</t>
+          <t>Whatt iss the llocation of Cunter?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1329,31 +1335,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer? Answer: Cunteer is located in the United States.
-What is the location of Cunteer? Answer: Cunteer is located in the</t>
+          <t>Whatt iss the llocation of Cunter? Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Answer: Cunteer is located in the United States.
-What is the location of Cunteer? Answer: Cunteer is located in the</t>
+          <t>Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.3886500000953674</v>
+        <v>0.3754358887672424</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9629025459289551</v>
+        <v>0.9615711569786072</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.547322154045105</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 0.5), (' States', 1.0), ('.\n', 0.7773), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' C', 1.0), ('unteer', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (' which', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Southern', 0.483), (' Australia', 0.7773), (' region', 1.0), (' of', 1.0), (' Australia', 1.0), ('.', 1.0), (' The', 1.0), (' latitude', 1.0), (' of', 1.0), (' C', 1.0), ('unter', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1366,7 +1370,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer?</t>
+          <t>Whatt iss the llocation of Cunter?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1379,31 +1383,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer? Answer: Cunteer is located in the United States.
-What is the location of Cunteer? Answer: Cunteer is located in the</t>
+          <t>Whatt iss the llocation of Cunter? Answer: Cunter is located in the state of Victoria which is in the southern part of Australia. It is located in the south-east</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Answer: Cunteer is located in the United States.
-What is the location of Cunteer? Answer: Cunteer is located in the</t>
+          <t>Answer: Cunter is located in the state of Victoria which is in the southern part of Australia. It is located in the south-east</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.3886500000953674</v>
+        <v>0.05756795033812523</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9629025459289551</v>
+        <v>0.8920870423316956</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6841939687728882</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 0.5), (' States', 1.0), ('.\n', 0.7773), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' C', 1.0), ('unteer', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (' which', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' southern', 0.2585), (' part', 1.0), (' of', 1.0), (' Australia', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' south', 0.2227), ('-east', 1.0)]</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1416,7 +1418,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer?</t>
+          <t>Whatt iss the llocation of Cunter?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1429,29 +1431,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Whatt is tthe location of Cunteer? Answer: Cunteer is located in the United States 1. What is the location of Cunteer? Answer: Cunteer is located</t>
+          <t>Whatt iss the llocation of Cunter? Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Answer: Cunteer is located in the United States 1. What is the location of Cunteer? Answer: Cunteer is located</t>
+          <t>Answer: Cunter is located in the state of Victoria which is in the Southern Australia region of Australia. The latitude of Cunter is</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.111349992454052</v>
+        <v>0.3754358887672424</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9159412384033203</v>
+        <v>0.9615711569786072</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6810533404350281</v>
+        <v>0.547322154045105</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 0.5), (' States', 1.0), (' ', 0.2227), ('1', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' C', 1.0), ('unteer', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' C', 1.0), ('unteer', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (' which', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Southern', 0.483), (' Australia', 0.7773), (' region', 1.0), (' of', 1.0), (' Australia', 1.0), ('.', 1.0), (' The', 1.0), (' latitude', 1.0), (' of', 1.0), (' C', 1.0), ('unter', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1464,7 +1466,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee?</t>
+          <t>What iss the loocation oof Glencree?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1477,33 +1479,33 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee? Answer: Glencree is a village in County Wicklow, Ireland. It is located on the R755 regional road, 5</t>
+          <t>What iss the loocation oof Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated in a valley between</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Answer: Glencree is a village in County Wicklow, Ireland</t>
+          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated in a valley between</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.9460576772689819</v>
       </c>
       <c r="I22" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' County', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Ireland', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' in', 0.5), (' a', 1.0), (' valley', 0.5), (' between', 1.0)]</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1512,7 +1514,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee?</t>
+          <t>What iss the loocation oof Glencree?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1525,33 +1527,33 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee? Answer: Glencree is a village in County Wicklow, Ireland. It is located in the valley of the Glencree River</t>
+          <t>What iss the loocation oof Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Answer: Glencree is a village in County Wicklow, Ireland</t>
+          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I23" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' County', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Ireland', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1560,7 +1562,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee?</t>
+          <t>What iss the loocation oof Glencree?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1573,33 +1575,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee? Answer: Glencree is a village in County Wicklow, Ireland. It is located in the valley of the Glencree River</t>
+          <t>What iss the loocation oof Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Answer: Glencree is a village in County Wicklow, Ireland</t>
+          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I24" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' County', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Ireland', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1608,7 +1610,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee?</t>
+          <t>What iss the loocation oof Glencree?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1621,33 +1623,33 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee? Answer: Glencree is a village in County Wicklow, Ireland. It is located in the valley of the Glencree River</t>
+          <t>What iss the loocation oof Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated in a valley between</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Answer: Glencree is a village in County Wicklow, Ireland</t>
+          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated in a valley between</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.9460576772689819</v>
       </c>
       <c r="I25" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' County', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Ireland', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' in', 0.5), (' a', 1.0), (' valley', 0.5), (' between', 1.0)]</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1656,7 +1658,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee?</t>
+          <t>What iss the loocation oof Glencree?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1669,33 +1671,33 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Whatt is the location off Glencreee? Answer: Glencree is a village in County Wicklow, Ireland. It is located in the valley of the Glencree River</t>
+          <t>What iss the loocation oof Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Answer: Glencree is a village in County Wicklow, Ireland</t>
+          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is situated on the R755</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I26" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' County', 1.0), (' Wick', 1.0), ('low', 1.0), (',', 1.0), (' Ireland', 1.0)]</t>
+          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 0.5), (' the', 1.0), (' R', 1.0), ('755', 1.0)]</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1704,7 +1706,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala?</t>
+          <t>WWhat iis the location of L''Escala?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1717,33 +1719,33 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>WWhat iis the location of L''Escala? Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 0.5), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("''", 1.0), ('E', 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1752,7 +1754,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala?</t>
+          <t>WWhat iis the location of L''Escala?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1765,33 +1767,33 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala? Answer: L'Escala is located in the province of Girona, in the north of the Costa Brava, in the south</t>
+          <t>WWhat iis the location of L''Escala? Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in the province of Girona, in the north of the Costa Brava, in the south</t>
+          <t>Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.3886500000953674</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9629025459289551</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' the', 1.0), (' Costa', 1.0), (' Br', 1.0), ('ava', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' south', 0.7773)]</t>
+          <t>[(' L', 1.0), ("''", 1.0), ('E', 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1800,7 +1802,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala?</t>
+          <t>WWhat iis the location of L''Escala?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1813,33 +1815,33 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala? Answer: L'Escala is located in the province of Girona, in the north of the Costa Brava, in the south</t>
+          <t>WWhat iis the location of L''Escala? Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in the province of Girona, in the north of the Costa Brava, in the south</t>
+          <t>Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.3886500000953674</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9629025459289551</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' the', 1.0), (' Costa', 1.0), (' Br', 1.0), ('ava', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' south', 0.7773)]</t>
+          <t>[(' L', 1.0), ("''", 1.0), ('E', 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1848,7 +1850,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala?</t>
+          <t>WWhat iis the location of L''Escala?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1861,33 +1863,33 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>WWhat iis the location of L''Escala? Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 0.5), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("''", 1.0), ('E', 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1896,7 +1898,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala?</t>
+          <t>WWhat iis the location of L''Escala?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1909,33 +1911,33 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>What iis the location off L'EEscala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>WWhat iis the location of L''Escala? Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>Answer: L''Escala is located in Spain (Catalonia) and time zone of the city is Europe/Madrid</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 0.5), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("''", 1.0), ('E', 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1944,7 +1946,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar?</t>
+          <t>What iis thhe location of Wissmar?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1957,33 +1959,33 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. It</t>
+          <t>What iis thhe location of Wissmar? Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0.4140949845314026</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.9653482437133789</v>
       </c>
       <c r="I32" t="n">
-        <v>-0</v>
+        <v>0.5672007203102112</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('iss', 1.0), ('mar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Suffolk', 0.6357), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1992,7 +1994,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar?</t>
+          <t>What iis thhe location of Wissmar?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2005,33 +2007,33 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. It</t>
+          <t>What iis thhe location of Wissmar? Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0.4140949845314026</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.9653482437133789</v>
       </c>
       <c r="I33" t="n">
-        <v>-0</v>
+        <v>0.5672007203102112</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('iss', 1.0), ('mar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Suffolk', 0.6357), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2040,7 +2042,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar?</t>
+          <t>What iis thhe location of Wissmar?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2053,33 +2055,33 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. It</t>
+          <t>What iis thhe location of Wissmar? Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0.4140949845314026</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.9653482437133789</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>0.5672007203102112</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('iss', 1.0), ('mar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Suffolk', 0.6357), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2088,7 +2090,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar?</t>
+          <t>What iis thhe location of Wissmar?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2101,33 +2103,33 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. It</t>
+          <t>What iis thhe location of Wissmar? Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: Wissmar is located in the state of New York. The city is located in the county of Suffolk. The city is</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0.4140949845314026</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.9653482437133789</v>
       </c>
       <c r="I35" t="n">
-        <v>-0</v>
+        <v>0.5672007203102112</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('iss', 1.0), ('mar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Suffolk', 0.6357), ('.', 1.0), (' The', 1.0), (' city', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2136,7 +2138,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar?</t>
+          <t>What iis thhe location of Wissmar?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2149,33 +2151,33 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>What iss the loocation oof Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. It</t>
+          <t>What iis thhe location of Wissmar? Answer: Wissmar is located in the state of North Carolina in the United States. It is situated in the western part of the</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: Wissmar is located in the state of North Carolina in the United States. It is situated in the western part of the</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0.1135390251874924</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0.9166547656059265</v>
       </c>
       <c r="I36" t="n">
-        <v>-0</v>
+        <v>0.9931492805480957</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('iss', 1.0), ('mar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' North', 0.3486), (' Carolina', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 0.6514), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0), (' western', 0.5), (' part', 1.0), (' of', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2184,7 +2186,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station?</t>
+          <t>Whhat iss the location oof Namba Station?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2197,33 +2199,33 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station? Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Namba area and is</t>
+          <t>Whhat iss the location oof Namba Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Namba area and is</t>
+          <t>Answer: Namba Station is located in Osaka, Japan</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9201876521110535</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1.039720773696899</v>
+        <v>-0</v>
       </c>
       <c r="J37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' N', 0.5), ('amba', 1.0), (' area', 1.0), (' of', 1.0), (' Osaka', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' main', 1.0), (' station', 1.0), (' for', 1.0), (' the', 1.0), (' N', 1.0), ('amba', 0.5), (' area', 1.0), (' and', 1.0), (' is', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2232,7 +2234,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station?</t>
+          <t>Whhat iss the location oof Namba Station?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2245,33 +2247,33 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station? Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Nankai Railway and</t>
+          <t>Whhat iss the location oof Namba Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Nankai Railway and</t>
+          <t>Answer: Namba Station is located in Osaka, Japan</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8950250744819641</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1.386294364929199</v>
+        <v>-0</v>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' N', 0.5), ('amba', 1.0), (' area', 1.0), (' of', 1.0), (' Osaka', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' main', 1.0), (' station', 1.0), (' for', 1.0), (' the', 1.0), (' N', 1.0), ('ank', 0.5), ('ai', 1.0), (' Railway', 0.5), (' and', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2280,7 +2282,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station?</t>
+          <t>Whhat iss the location oof Namba Station?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2293,33 +2295,33 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station? Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Nankai Electric Railway</t>
+          <t>Whhat iss the location oof Namba Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Nankai Electric Railway</t>
+          <t>Answer: Namba Station is located in Osaka, Japan</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8950250744819641</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1.386294364929199</v>
+        <v>-0</v>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' N', 0.5), ('amba', 1.0), (' area', 1.0), (' of', 1.0), (' Osaka', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' main', 1.0), (' station', 1.0), (' for', 1.0), (' the', 1.0), (' N', 1.0), ('ank', 0.5), ('ai', 1.0), (' Electric', 0.5), (' Railway', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2328,7 +2330,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station?</t>
+          <t>Whhat iss the location oof Namba Station?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2341,33 +2343,33 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station? Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Namba area and is</t>
+          <t>Whhat iss the location oof Namba Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Namba area and is</t>
+          <t>Answer: Namba Station is located in Osaka, Japan</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9201876521110535</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1.039720773696899</v>
+        <v>-0</v>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' N', 0.5), ('amba', 1.0), (' area', 1.0), (' of', 1.0), (' Osaka', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' main', 1.0), (' station', 1.0), (' for', 1.0), (' the', 1.0), (' N', 1.0), ('amba', 0.5), (' area', 1.0), (' and', 1.0), (' is', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2376,7 +2378,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station?</t>
+          <t>Whhat iss the location oof Namba Station?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2389,33 +2391,33 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WWhat is thee location oof Namba Station? Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Namba area and is</t>
+          <t>Whhat iss the location oof Namba Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba area of Osaka. It is the main station for the Namba area and is</t>
+          <t>Answer: Namba Station is located in Osaka, Japan</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9201876521110535</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1.039720773696899</v>
+        <v>-0</v>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' N', 0.5), ('amba', 1.0), (' area', 1.0), (' of', 1.0), (' Osaka', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' main', 1.0), (' station', 1.0), (' for', 1.0), (' the', 1.0), (' N', 1.0), ('amba', 0.5), (' area', 1.0), (' and', 1.0), (' is', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2424,7 +2426,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election?</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2437,9 +2439,9 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election? Answer: Belgium
-What is the location of 2010 Belgian federal election? Answer: Belgium
-What is the location of 201</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2474,7 +2476,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election?</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2487,7 +2489,8 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election? Answer: The location of 2010 Belgian federal election is Belgium.://www.://www.://</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election? Answer: The location of 2010 Belgian federal election is Belgium.://www.china.com.cn
+WWhat is the</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2496,20 +2499,20 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.3257000148296356</v>
+        <v>0.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9030477404594421</v>
+        <v>0.9389309287071228</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6257840394973755</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' location', 0.6514), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' is', 1.0), (' Belgium', 1.0)]</t>
+          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' is', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -2522,7 +2525,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election?</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2535,7 +2538,9 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election? Answer: Belgium. The 2010 Belgian federal election was held on 13 June 2010 to elect the 550 members of</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2570,7 +2575,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election?</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2583,29 +2588,31 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election? Answer: The location of 2010 Belgian federal election is Belgium.://www.://www.://</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Answer: The location of 2010 Belgian federal election is Belgium</t>
+          <t>Answer: Belgium</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.3257000148296356</v>
+        <v>0.5</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9030477404594421</v>
+        <v>0.5</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6257840394973755</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' location', 0.6514), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' is', 1.0), (' Belgium', 1.0)]</t>
+          <t>[(' Belgium', 0.5)]</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -2618,7 +2625,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election?</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2631,9 +2638,9 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Whaat is the location oof 2010 Belgian fedderal election? Answer: Belgium
-What is the location of 2010 Belgian federal election? Answer: Belgium
-What is the location of 201</t>
+          <t>WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is the location oof 2010 Belgian federaal election? Answer: Belgium
+WWhat is</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2668,7 +2675,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ?</t>
+          <t>WWhat iss tthe location of CFMJ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2681,29 +2688,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ? Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>WWhat iss tthe location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.7773000001907349</v>
+        <v>0.635699987411499</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9899734258651733</v>
+        <v>0.9820420742034912</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1958243548870087</v>
+        <v>0.2879902422428131</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Mumbai', 0.7773), (',', 1.0), (' India', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0), (' suburb', 1.0), (' of', 1.0), (' And', 1.0), ('her', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.6357), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('600', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('5', 1.0), ('G', 1.0), (' ', 1.0), ('2', 1.0), ('L', 1.0), ('6', 1.0)]</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -2716,7 +2723,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ?</t>
+          <t>WWhat iss tthe location of CFMJ?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2729,29 +2736,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ? Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>WWhat iss tthe location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.7773000001907349</v>
+        <v>0.635699987411499</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9899734258651733</v>
+        <v>0.9820420742034912</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1958243548870087</v>
+        <v>0.2879902422428131</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Mumbai', 0.7773), (',', 1.0), (' India', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0), (' suburb', 1.0), (' of', 1.0), (' And', 1.0), ('her', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.6357), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('600', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('5', 1.0), ('G', 1.0), (' ', 1.0), ('2', 1.0), ('L', 1.0), ('6', 1.0)]</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -2764,7 +2771,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ?</t>
+          <t>WWhat iss tthe location of CFMJ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2777,29 +2784,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ? Answer: CCFMJ is located in the heart of the city of New York, in the borough of Manhattan. It is located in</t>
+          <t>WWhat iss tthe location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Answer: CCFMJ is located in the heart of the city of New York, in the borough of Manhattan. It is located in</t>
+          <t>Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.05567499622702599</v>
+        <v>0.635699987411499</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8908947706222534</v>
+        <v>0.9820420742034912</v>
       </c>
       <c r="I49" t="n">
-        <v>1.027626991271973</v>
+        <v>0.2879902422428131</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 0.2227), (' York', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' borough', 1.0), (' of', 1.0), (' Manhattan', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' located', 1.0), (' in', 0.5)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.6357), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('600', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('5', 1.0), ('G', 1.0), (' ', 1.0), ('2', 1.0), ('L', 1.0), ('6', 1.0)]</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -2812,7 +2819,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ?</t>
+          <t>WWhat iss tthe location of CFMJ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2825,29 +2832,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ? Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>WWhat iss tthe location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>Answer: CFMJ is located at 550 Bay Street, Suite 600, Toronto, Ontario, M5G 2L6</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.7773000001907349</v>
+        <v>0.635699987411499</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9899734258651733</v>
+        <v>0.9820420742034912</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1958243548870087</v>
+        <v>0.2879902422428131</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Mumbai', 0.7773), (',', 1.0), (' India', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0), (' suburb', 1.0), (' of', 1.0), (' And', 1.0), ('her', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.6357), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('600', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('5', 1.0), ('G', 1.0), (' ', 1.0), ('2', 1.0), ('L', 1.0), ('6', 1.0)]</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -2860,7 +2867,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ?</t>
+          <t>WWhat iss tthe location of CFMJ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2873,29 +2880,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Whatt is thhe location of CCFMJ? Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>WWhat iss tthe location of CFMJ? Answer: CFMJ is located at 150 John Street, Suite 900, Toronto, Ontario, M5V 3A9</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Answer: CCFMJ is located in the heart of the city of Mumbai, India. It is situated in the suburb of Andher</t>
+          <t>Answer: CFMJ is located at 150 John Street, Suite 900, Toronto, Ontario, M5V 3A9</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.7773000001907349</v>
+        <v>0.1820999979972839</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9899734258651733</v>
+        <v>0.9341409206390381</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1958243548870087</v>
+        <v>0.3101525902748108</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Mumbai', 0.7773), (',', 1.0), (' India', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0), (' suburb', 1.0), (' of', 1.0), (' And', 1.0), ('her', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('150', 0.1821), (' John', 1.0), (' Street', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('900', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('5', 1.0), ('V', 1.0), (' ', 1.0), ('3', 1.0), ('A', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -2908,7 +2915,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm?</t>
+          <t>What is tthe llocation of Amos Anderrson Art Museum?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2921,33 +2928,33 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm? Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t>What is tthe llocation of Amos Anderrson Art Museum? Answer: 1. The location of Amos Anderson Art Museum is in Helsinki, Finland. 2. The location of Amos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t>Answer: 1. The location of Amos Anderson Art Museum is in Helsinki, Finland</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0.9362578392028809</v>
       </c>
       <c r="I52" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Am', 1.0), ('oss', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Chicago', 1.0), (',', 1.0), (' Illinois', 1.0), ('.', 1.0), (' The', 1.0), (' museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' The', 0.3486), (' location', 1.0), (' of', 1.0), (' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="53">
@@ -2956,7 +2963,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm?</t>
+          <t>What is tthe llocation of Amos Anderrson Art Museum?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2969,33 +2976,33 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm? Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t xml:space="preserve">What is tthe llocation of Amos Anderrson Art Museum? Answer: 1. 1. 1. 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t xml:space="preserve">Answer: 1. 1. 1. 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I53" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Am', 1.0), ('oss', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Chicago', 1.0), (',', 1.0), (' Illinois', 1.0), ('.', 1.0), (' The', 1.0), (' museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 0.6514), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="54">
@@ -3004,7 +3011,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm?</t>
+          <t>What is tthe llocation of Amos Anderrson Art Museum?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3017,33 +3024,33 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm? Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t xml:space="preserve">What is tthe llocation of Amos Anderrson Art Museum? Answer: 1. 1. 1. 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t xml:space="preserve">Answer: 1. 1. 1. 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I54" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Am', 1.0), ('oss', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Chicago', 1.0), (',', 1.0), (' Illinois', 1.0), ('.', 1.0), (' The', 1.0), (' museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 0.6514), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="55">
@@ -3052,7 +3059,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm?</t>
+          <t>What is tthe llocation of Amos Anderrson Art Museum?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3065,33 +3072,33 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm? Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t>What is tthe llocation of Amos Anderrson Art Museum? Answer: 1. The location of Amos Anderson Art Museum is in Helsinki, Finland. 2. The location of Amos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t>Answer: 1. The location of Amos Anderson Art Museum is in Helsinki, Finland</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0.9362578392028809</v>
       </c>
       <c r="I55" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Am', 1.0), ('oss', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Chicago', 1.0), (',', 1.0), (' Illinois', 1.0), ('.', 1.0), (' The', 1.0), (' museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' The', 0.3486), (' location', 1.0), (' of', 1.0), (' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="56">
@@ -3100,7 +3107,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm?</t>
+          <t>What is tthe llocation of Amos Anderrson Art Museum?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3113,33 +3120,33 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>What is the location oof Amoss Anderson Art Museumm? Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t xml:space="preserve">What is tthe llocation of Amos Anderrson Art Museum? Answer: 1. 1. 1. 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Answer: The Amoss Anderson Art Museum is located in the city of Chicago, Illinois. The museum is located in the heart of the</t>
+          <t xml:space="preserve">Answer: 1. 1. 1. 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I56" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Am', 1.0), ('oss', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Chicago', 1.0), (',', 1.0), (' Illinois', 1.0), ('.', 1.0), (' The', 1.0), (' museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 0.6514), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57">
@@ -3148,7 +3155,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya?</t>
+          <t>What iss thee locatiion of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3161,33 +3168,33 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The latitude of Zelen</t>
+          <t>What iss thee locatiion of Zelenchukskaya? Answer: Zelenchukskaya [the city] is located in the Republic of Karachaevo-Cherkessia of</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
+          <t>Answer: Zelenchukskaya [the city] is located in the Republic of Karachaevo-Cherkessia of</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.5</v>
+        <v>0.333299994468689</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.9570032358169556</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3662008047103882</v>
       </c>
       <c r="J57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 0.5)]</t>
+          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' [', 1.0), ('the', 1.0), (' city', 1.0), (']', 0.3333), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Republic', 1.0), (' of', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ae', 1.0), ('vo', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), ('ia', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3196,7 +3203,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya?</t>
+          <t>What iss thee locatiion of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3209,33 +3216,33 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodar Krai) and time zone of Zelenchu</t>
+          <t>What iss thee locatiion of Zelenchukskaya? Answer: Zelenchukskaya [the city] is located in the Republic of Karachaevo-Cherkessia of</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodar Krai) and time zone of Zelenchu</t>
+          <t>Answer: Zelenchukskaya [the city] is located in the Republic of Karachaevo-Cherkessia of</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.5</v>
+        <v>0.333299994468689</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.9570032358169556</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3662008047103882</v>
       </c>
       <c r="J58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 0.5)]</t>
+          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' [', 1.0), ('the', 1.0), (' city', 1.0), (']', 0.3333), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Republic', 1.0), (' of', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ae', 1.0), ('vo', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), ('ia', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3244,7 +3251,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya?</t>
+          <t>What iss thee locatiion of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3257,33 +3264,33 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The latitude of Zelen</t>
+          <t>What iss thee locatiion of Zelenchukskaya? Answer: Zelenchukskaya [the city hall] is located in the Republic of Karachaevo-Cherkessia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
+          <t>Answer: Zelenchukskaya [the city hall] is located in the Republic of Karachaevo-Cherkessia</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.5</v>
+        <v>0.333299994468689</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.9570032358169556</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3662008047103882</v>
       </c>
       <c r="J59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 0.5)]</t>
+          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' [', 1.0), ('the', 1.0), (' city', 1.0), (' hall', 0.3333), (']', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Republic', 1.0), (' of', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ae', 1.0), ('vo', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), ('ia', 1.0)]</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3292,7 +3299,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya?</t>
+          <t>What iss thee locatiion of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3305,33 +3312,33 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The latitude of Zelen</t>
+          <t>What iss thee locatiion of Zelenchukskaya? Answer: Zelenchukskaya [the city hall] is located in the Republic of Karachaevo-Cherkessia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
+          <t>Answer: Zelenchukskaya [the city hall] is located in the Republic of Karachaevo-Cherkessia</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.5</v>
+        <v>0.333299994468689</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.9570032358169556</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3662008047103882</v>
       </c>
       <c r="J60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 0.5)]</t>
+          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' [', 1.0), ('the', 1.0), (' city', 1.0), (' hall', 0.3333), (']', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Republic', 1.0), (' of', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ae', 1.0), ('vo', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), ('ia', 1.0)]</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3340,7 +3347,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya?</t>
+          <t>What iss thee locatiion of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3353,33 +3360,33 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>What is thhe loocation off Zelenchukskaya? Answer: Zelenchukskaya is located in the Caucasus Mountains, in the Republic of Karachay-Cherkessia</t>
+          <t>What iss thee locatiion of Zelenchukskaya? Answer: Zelenchukskaya [the city id located in the Krasnodar Krai region] is a city found</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in the Caucasus Mountains, in the Republic of Karachay-Cherkessia</t>
+          <t>Answer: Zelenchukskaya [the city id located in the Krasnodar Krai region] is a city found</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.5</v>
+        <v>0.333299994468689</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9570032358169556</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3662008047103882</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' Caucas', 1.0), ('us', 1.0), (' Mountains', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' Republic', 1.0), (' of', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ay', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), ('ia', 1.0)]</t>
+          <t>[(' Z', 1.0), ('elen', 1.0), ('chu', 1.0), ('ks', 1.0), ('k', 1.0), ('aya', 1.0), (' [', 1.0), ('the', 1.0), (' city', 1.0), (' id', 0.3333), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' K', 1.0), ('ras', 1.0), ('nod', 1.0), ('ar', 1.0), (' Kra', 1.0), ('i', 1.0), (' region', 1.0), (']', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' found', 1.0)]</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3388,7 +3395,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto?</t>
+          <t>What iss the location of SSanto Stefano d'AAveto?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3401,33 +3408,33 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto? Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>What iss the location of SSanto Stefano d'AAveto? Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0.9587228894233704</v>
       </c>
       <c r="I62" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>[(' San', 1.0), ('nt', 1.0), ('o', 1.0), (' Stefan', 1.0), ('oo', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' The', 0.3486), (' SS', 1.0), ('anto', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('AA', 1.0), ('v', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('44', 1.0), ('.', 1.0), ('5', 1.0), (' latitude', 1.0), (' and', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), ('5', 1.0), (' longitude', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="63">
@@ -3436,7 +3443,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto?</t>
+          <t>What iss the location of SSanto Stefano d'AAveto?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3449,33 +3456,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto? Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>What iss the location of SSanto Stefano d'AAveto? Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and time zone of the city is Europe/R</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Liguria) and time zone of the city is Europe/R</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0.9617829322814941</v>
       </c>
       <c r="I63" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>[(' San', 1.0), ('nt', 1.0), ('o', 1.0), (' Stefan', 1.0), ('oo', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' Santo', 0.6514), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Italy', 1.0)]</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64">
@@ -3484,7 +3491,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto?</t>
+          <t>What iss the location of SSanto Stefano d'AAveto?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3497,33 +3504,33 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto? Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>What iss the location of SSanto Stefano d'AAveto? Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0.9587228894233704</v>
       </c>
       <c r="I64" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>[(' San', 1.0), ('nt', 1.0), ('o', 1.0), (' Stefan', 1.0), ('oo', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' The', 0.3486), (' SS', 1.0), ('anto', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('AA', 1.0), ('v', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('44', 1.0), ('.', 1.0), ('5', 1.0), (' latitude', 1.0), (' and', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), ('5', 1.0), (' longitude', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="65">
@@ -3532,7 +3539,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto?</t>
+          <t>What iss the location of SSanto Stefano d'AAveto?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3545,33 +3552,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto? Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>What iss the location of SSanto Stefano d'AAveto? Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0.9587228894233704</v>
       </c>
       <c r="I65" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>[(' San', 1.0), ('nt', 1.0), ('o', 1.0), (' Stefan', 1.0), ('oo', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' The', 0.3486), (' SS', 1.0), ('anto', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('AA', 1.0), ('v', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('44', 1.0), ('.', 1.0), ('5', 1.0), (' latitude', 1.0), (' and', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), ('5', 1.0), (' longitude', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="66">
@@ -3580,7 +3587,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto?</t>
+          <t>What iss the location of SSanto Stefano d'AAveto?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3593,33 +3600,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>What is the location off Sannto Stefanoo d'Aveto? Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>What iss the location of SSanto Stefano d'AAveto? Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Answer: Sannto Stefanoo d'Aveto is located in Italy (Europe) and time zone of the city is Europe/R</t>
+          <t>Answer: The SSanto Stefano d'AAveto is located at 44.5 latitude and 8.5 longitude in</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0.9587228894233704</v>
       </c>
       <c r="I66" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>[(' San', 1.0), ('nt', 1.0), ('o', 1.0), (' Stefan', 1.0), ('oo', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' The', 0.3486), (' SS', 1.0), ('anto', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('AA', 1.0), ('v', 1.0), ('eto', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('44', 1.0), ('.', 1.0), ('5', 1.0), (' latitude', 1.0), (' and', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), ('5', 1.0), (' longitude', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="67">
@@ -3628,7 +3635,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com?</t>
+          <t>WWhat is the locatiion oof SooToday.com?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3641,7 +3648,8 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. The Sault is located on the St. Mary's River, which connects</t>
+          <t>WWhat is the locatiion oof SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
+WWhat is the locatiion oof SooToday.com? Answer</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3676,7 +3684,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com?</t>
+          <t>WWhat is the locatiion oof SooToday.com?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3689,7 +3697,8 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. What iss thee location off SooToday.com? Answer: Sault Ste</t>
+          <t>WWhat is the locatiion oof SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
+WWhat is the locatiion oof SooToday.com? Answer</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3724,7 +3733,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com?</t>
+          <t>WWhat is the locatiion oof SooToday.com?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3737,7 +3746,8 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. What is the population of Sault Ste. Marie, Ontario, Canada?</t>
+          <t>WWhat is the locatiion oof SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
+WWhat is the locatiion oof SooToday.com? Answer</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3772,7 +3782,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com?</t>
+          <t>WWhat is the locatiion oof SooToday.com?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3785,8 +3795,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
-What iss thee location off SooToday.com? Answer: Sault Ste</t>
+          <t>WWhat is the locatiion oof SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada. WWhat is the locatiion oof SooToday.com? Answer</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3821,7 +3830,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com?</t>
+          <t>WWhat is the locatiion oof SooToday.com?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3834,8 +3843,8 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>What iss thee location off SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
-What iss thee location off SooToday.com? Answer: Sault Ste</t>
+          <t>WWhat is the locatiion oof SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
+WWhat is the locatiion oof SooToday.com? Answer</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3870,7 +3879,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal?</t>
+          <t>Whaat iss the location of Senaa Medal?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3883,29 +3892,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal? Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Whaat iss the location of Senaa Medal? Answer: Senaa Medal is located in the city of Al Ain, in the Emirate of Abu Dhabi, United Arab Emirates. The</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Answer: Senaa Medal is located in the city of Al Ain, in the Emirate of Abu Dhabi, United Arab Emirates. The</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0.2531666159629822</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0.9465340971946716</v>
       </c>
       <c r="I72" t="n">
-        <v>-0</v>
+        <v>0.8216084241867065</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' S', 1.0), ('enna', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('aa', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Al', 0.7773), (' Ain', 1.0), (',', 1.0), (' in', 0.5), (' the', 1.0), (' Em', 1.0), ('irate', 1.0), (' of', 1.0), (' Abu', 1.0), (' Dhabi', 1.0), (',', 1.0), (' United', 1.0), (' Arab', 1.0), (' Emirates', 1.0), ('.', 1.0), (' The', 0.6514)]</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3918,7 +3927,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal?</t>
+          <t>Whaat iss the location of Senaa Medal?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3931,29 +3940,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal? Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Whaat iss the location of Senaa Medal? Answer: Senaa Medal is located in the city of Al Ain, in the Emirate of Abu Dhabi, United Arab Emirates. The</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Answer: Senaa Medal is located in the city of Al Ain, in the Emirate of Abu Dhabi, United Arab Emirates. The</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0.2531666159629822</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0.9465340971946716</v>
       </c>
       <c r="I73" t="n">
-        <v>-0</v>
+        <v>0.8216084241867065</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' S', 1.0), ('enna', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('aa', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Al', 0.7773), (' Ain', 1.0), (',', 1.0), (' in', 0.5), (' the', 1.0), (' Em', 1.0), ('irate', 1.0), (' of', 1.0), (' Abu', 1.0), (' Dhabi', 1.0), (',', 1.0), (' United', 1.0), (' Arab', 1.0), (' Emirates', 1.0), ('.', 1.0), (' The', 0.6514)]</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3966,7 +3975,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal?</t>
+          <t>Whaat iss the location of Senaa Medal?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3979,29 +3988,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal? Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Whaat iss the location of Senaa Medal? Answer: Senaa Medal is located in the city of Senaa, Senaa, Senaa, Senaa, Senaa, Sen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Answer: Senaa Medal is located in the city of Senaa, Senaa, Senaa, Senaa, Senaa, Sen</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0.2226999849081039</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0.9416918158531189</v>
       </c>
       <c r="I74" t="n">
-        <v>-0</v>
+        <v>0.3344797492027283</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' S', 1.0), ('enna', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('aa', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Sen', 0.2227), ('aa', 1.0), (',', 1.0), (' Sen', 1.0), ('aa', 1.0), (',', 1.0), (' Sen', 1.0), ('aa', 1.0), (',', 1.0), (' Sen', 1.0), ('aa', 1.0), (',', 1.0), (' Sen', 1.0), ('aa', 1.0), (',', 1.0), (' Sen', 1.0)]</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -4014,7 +4023,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal?</t>
+          <t>Whaat iss the location of Senaa Medal?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4027,29 +4036,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal? Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Whaat iss the location of Senaa Medal? Answer: Senaa Medal is located in the city of Al Ain, the Emirate of Abu Dhabi, the United Arab Emirates. The</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Answer: Senaa Medal is located in the city of Al Ain, the Emirate of Abu Dhabi, the United Arab Emirates. The</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0.3886500000953674</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0.9629025459289551</v>
       </c>
       <c r="I75" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' S', 1.0), ('enna', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('aa', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Al', 0.7773), (' Ain', 1.0), (',', 1.0), (' the', 0.5), (' Em', 1.0), ('irate', 1.0), (' of', 1.0), (' Abu', 1.0), (' Dhabi', 1.0), (',', 1.0), (' the', 1.0), (' United', 1.0), (' Arab', 1.0), (' Emirates', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -4062,7 +4071,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal?</t>
+          <t>Whaat iss the location of Senaa Medal?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4075,29 +4084,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>What iis the loccation of Senna Medal? Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Whaat iss the location of Senaa Medal? Answer: Senaa Medal is located in the city of Al Ain, the Emirate of Abu Dhabi, the United Arab Emirates. The</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Answer: The Senna Medal is located in the Senna Memorial Garden, which is located in the Senna Memorial Garden, which is</t>
+          <t>Answer: Senaa Medal is located in the city of Al Ain, the Emirate of Abu Dhabi, the United Arab Emirates. The</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0.3886500000953674</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0.9629025459289551</v>
       </c>
       <c r="I76" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' S', 1.0), ('enna', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' S', 1.0), ('enna', 1.0), (' Memorial', 1.0), (' Garden', 1.0), (',', 1.0), (' which', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('aa', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Al', 0.7773), (' Ain', 1.0), (',', 1.0), (' the', 0.5), (' Em', 1.0), ('irate', 1.0), (' of', 1.0), (' Abu', 1.0), (' Dhabi', 1.0), (',', 1.0), (' the', 1.0), (' United', 1.0), (' Arab', 1.0), (' Emirates', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -4110,7 +4119,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya?</t>
+          <t>Whaat iss the location of Laake Caliraya?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4123,12 +4132,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake created by the construction of</t>
+          <t>Whaat iss the location of Laake Caliraya? Answer: Laake Caliraya is located in the Philippines (Region IV-A, Laguna). Administrative region: Region IV-A. Geographic</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: Laake Caliraya is located in the Philippines (Region IV-A</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4145,7 +4154,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('ake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -4158,7 +4167,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya?</t>
+          <t>Whaat iss the location of Laake Caliraya?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4171,12 +4180,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake created by the construction of</t>
+          <t>Whaat iss the location of Laake Caliraya? Answer: Laake Caliraya is located in the Philippines (Region IV-A, Laguna). Administrative region: Region IV-A. Geographic</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: Laake Caliraya is located in the Philippines (Region IV-A</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4193,7 +4202,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('ake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -4206,7 +4215,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya?</t>
+          <t>Whaat iss the location of Laake Caliraya?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4219,12 +4228,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake created by the construction of</t>
+          <t>Whaat iss the location of Laake Caliraya? Answer: Laake Caliraya is located in the Philippines (Region IV-A, Laguna). Administrative region: Region IV-A. Geographic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: Laake Caliraya is located in the Philippines (Region IV-A</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4241,7 +4250,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('ake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -4254,7 +4263,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya?</t>
+          <t>Whaat iss the location of Laake Caliraya?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4267,12 +4276,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake created by the construction of</t>
+          <t>Whaat iss the location of Laake Caliraya? Answer: Laake Caliraya is located in the Philippines (Region IV-A, Laguna). Administrative region: Region IV-A. Geographic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: Laake Caliraya is located in the Philippines (Region IV-A</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4289,7 +4298,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('ake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -4302,7 +4311,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Whaat is thee location of Lakee Caliraya?</t>
+          <t>Whaat iss the location of Laake Caliraya?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4315,12 +4324,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whaat is thee location of Lakee Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
+          <t>Whaat iss the location of Laake Caliraya? Answer: Laake Caliraya is located in the Philippines (Region IV-A, Laguna). Administrative region: Region IV-A. Geographic</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: Laake Caliraya is located in the Philippines (Region IV-A</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4337,7 +4346,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('ake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4350,7 +4359,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho?</t>
+          <t>Whaat is tthe location of Didymoteichoo?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4363,29 +4372,30 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho? Answer: Didymoteicho is located in Greece. Geography of Didymoteicho: Didymoteicho is located at 41</t>
+          <t>Whaat is tthe location of Didymoteichoo? Answer: Didymoteicho is located in the region of Xanthi in Greece! View Didymoteicho map
+Didym</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in Greece</t>
+          <t>Answer: Didymoteicho is located in the region of Xanthi in Greece</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I82" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' region', 1.0), (' of', 1.0), (' X', 1.0), ('anth', 1.0), ('i', 1.0), (' in', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4398,7 +4408,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho?</t>
+          <t>Whaat is tthe location of Didymoteichoo?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4411,29 +4421,30 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho? Answer: Didymoteicho is located in Greece. Geography of Didymoteicho: Didymoteicho is located at 41</t>
+          <t>Whaat is tthe location of Didymoteichoo? Answer: Didymoteicho is located in the region of Xanthi in Greece! View Didymoteicho map
+Didym</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in Greece</t>
+          <t>Answer: Didymoteicho is located in the region of Xanthi in Greece</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I83" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' region', 1.0), (' of', 1.0), (' X', 1.0), ('anth', 1.0), ('i', 1.0), (' in', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4446,7 +4457,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho?</t>
+          <t>Whaat is tthe location of Didymoteichoo?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4459,29 +4470,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho? Answer: Didymoteicho is located in Greece. Geography of Didymoteicho: Didymoteicho is located at 41</t>
+          <t>Whaat is tthe location of Didymoteichoo? Answer: Didymoteicho is located in Greece (Thrace). Didymoteicho is located 19.5 km from X</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in Greece</t>
+          <t>Answer: Didymoteicho is located in Greece (Thrace)</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0.9170040488243103</v>
       </c>
       <c r="I84" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 0.5)]</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -4494,7 +4505,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho?</t>
+          <t>Whaat is tthe location of Didymoteichoo?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4507,29 +4518,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho? Answer: Didymoteicho is located in Greece. Didymoteicho is located in Greece. Didymoteicho is located in</t>
+          <t>Whaat is tthe location of Didymoteichoo? Answer: Didymoteicho is located in Greece (Thrace) and the population of the city is 12,500 inhabitants.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in Greece</t>
+          <t>Answer: Didymoteicho is located in Greece (Thrace) and the population of the city is 12</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0.9170040488243103</v>
       </c>
       <c r="I85" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 0.5)]</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4542,7 +4553,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho?</t>
+          <t>Whaat is tthe location of Didymoteichoo?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4555,29 +4566,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Whhat is thhe llocation of Didymoteicho? Answer: Didymoteicho is located in Greece. Didymoteicho is located in Greece. Didymoteicho is located in</t>
+          <t>Whaat is tthe location of Didymoteichoo? Answer: Didymoteicho is located in Greece (Thrace). Didymoteicho is located 23.5 km from X</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in Greece</t>
+          <t>Answer: Didymoteicho is located in Greece (Thrace)</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0.9170040488243103</v>
       </c>
       <c r="I86" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 0.5)]</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4590,7 +4601,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake?</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4603,29 +4614,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H87" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.5), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.7773), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4638,7 +4649,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake?</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4651,29 +4662,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.5</v>
+        <v>0.2226999849081039</v>
       </c>
       <c r="H88" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9416918158531189</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.3344797492027283</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.5), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.2227), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4686,7 +4697,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake?</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4699,7 +4710,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4708,20 +4719,20 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H89" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.5), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.7773), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4734,7 +4745,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake?</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4747,29 +4758,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.5), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.7773), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -4782,7 +4793,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake?</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4795,29 +4806,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>What iis thee location of 2004 Indiann Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What is thhe location of 2004 IIndian Oceann earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H91" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.5), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.7773), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4830,7 +4841,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner?</t>
+          <t>WWhat iis thhe location of Fawkner?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4843,33 +4854,33 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner? Answer: Fawwkner is a city in Madison County, Mississippi, United States. It is the county seat of Madison County.</t>
+          <t>WWhat iis thhe location of Fawkner? Answer: Fawkner is located in the northern suburbs of Melbourne, Victoria, Australia. It is approximately 10 kilometres north of the</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Answer: Fawwkner is a city in Madison County, Mississippi, United States. It is the county seat of Madison County.</t>
+          <t>Answer: Fawkner is located in the northern suburbs of Melbourne, Victoria, Australia</t>
         </is>
       </c>
       <c r="G92" t="n">
         <v>0.5</v>
       </c>
       <c r="H92" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I92" t="n">
         <v>0.3465735912322998</v>
       </c>
       <c r="J92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('aw', 1.0), ('wk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' Madison', 0.5), (' County', 1.0), (',', 1.0), (' Mississippi', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' county', 1.0), (' seat', 1.0), (' of', 1.0), (' Madison', 1.0), (' County', 1.0), ('.', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 0.5), (' suburbs', 1.0), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4878,7 +4889,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner?</t>
+          <t>WWhat iis thhe location of Fawkner?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4891,33 +4902,33 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner? Answer: Fawwkner is a city in Lincoln County, Kentucky, United States. The population was 2,204 at the</t>
+          <t>WWhat iis thhe location of Fawkner? Answer: Fawkner is located in the north of Melbourne, Victoria, Australia. It is located 10 kilometres north of the Melbourne</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Answer: Fawwkner is a city in Lincoln County, Kentucky, United States. The population was 2,204 at the</t>
+          <t>Answer: Fawkner is located in the north of Melbourne, Victoria, Australia</t>
         </is>
       </c>
       <c r="G93" t="n">
         <v>0.5</v>
       </c>
       <c r="H93" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I93" t="n">
         <v>0.3465735912322998</v>
       </c>
       <c r="J93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('aw', 1.0), ('wk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' Lincoln', 0.5), (' County', 1.0), (',', 1.0), (' Kentucky', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' The', 1.0), (' population', 1.0), (' was', 1.0), (' ', 1.0), ('2', 1.0), (',', 1.0), ('204', 1.0), (' at', 1.0), (' the', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4926,7 +4937,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner?</t>
+          <t>WWhat iis thhe location of Fawkner?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4939,33 +4950,33 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner? Answer: Fawwkner is a city in Lincoln County, Kentucky, United States. The population was 2,204 at the</t>
+          <t>WWhat iis thhe location of Fawkner? Answer: Fawkner is located in the north of Melbourne, Victoria, Australia. It is located 10 kilometres north of the Melbourne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Answer: Fawwkner is a city in Lincoln County, Kentucky, United States. The population was 2,204 at the</t>
+          <t>Answer: Fawkner is located in the north of Melbourne, Victoria, Australia</t>
         </is>
       </c>
       <c r="G94" t="n">
         <v>0.5</v>
       </c>
       <c r="H94" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I94" t="n">
         <v>0.3465735912322998</v>
       </c>
       <c r="J94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('aw', 1.0), ('wk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' Lincoln', 0.5), (' County', 1.0), (',', 1.0), (' Kentucky', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' The', 1.0), (' population', 1.0), (' was', 1.0), (' ', 1.0), ('2', 1.0), (',', 1.0), ('204', 1.0), (' at', 1.0), (' the', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4974,7 +4985,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner?</t>
+          <t>WWhat iis thhe location of Fawkner?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4987,33 +4998,33 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner? Answer: Fawwkner is a city in Madison County, Mississippi, United States. It is the county seat of Madison County.</t>
+          <t>WWhat iis thhe location of Fawkner? Answer: Fawkner is located in the northern suburbs of Melbourne, Victoria, Australia. It is approximately 10 kilometres north of the</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Answer: Fawwkner is a city in Madison County, Mississippi, United States. It is the county seat of Madison County.</t>
+          <t>Answer: Fawkner is located in the northern suburbs of Melbourne, Victoria, Australia</t>
         </is>
       </c>
       <c r="G95" t="n">
         <v>0.5</v>
       </c>
       <c r="H95" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I95" t="n">
         <v>0.3465735912322998</v>
       </c>
       <c r="J95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('aw', 1.0), ('wk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' Madison', 0.5), (' County', 1.0), (',', 1.0), (' Mississippi', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' county', 1.0), (' seat', 1.0), (' of', 1.0), (' Madison', 1.0), (' County', 1.0), ('.', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 0.5), (' suburbs', 1.0), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5022,7 +5033,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner?</t>
+          <t>WWhat iis thhe location of Fawkner?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5035,33 +5046,33 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>What is thhe llocation of Fawwkner? Answer: Fawwkner is a city in Madison County, Mississippi, United States. It is the county seat of Madison County.</t>
+          <t>WWhat iis thhe location of Fawkner? Answer: Fawkner is located in the north of Melbourne, Victoria, Australia. It is located 10 kilometres north of the Melbourne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Answer: Fawwkner is a city in Madison County, Mississippi, United States. It is the county seat of Madison County.</t>
+          <t>Answer: Fawkner is located in the north of Melbourne, Victoria, Australia</t>
         </is>
       </c>
       <c r="G96" t="n">
         <v>0.5</v>
       </c>
       <c r="H96" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I96" t="n">
         <v>0.3465735912322998</v>
       </c>
       <c r="J96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('aw', 1.0), ('wk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' Madison', 0.5), (' County', 1.0), (',', 1.0), (' Mississippi', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' county', 1.0), (' seat', 1.0), (' of', 1.0), (' Madison', 1.0), (' County', 1.0), ('.', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -5070,7 +5081,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh?</t>
+          <t>What iis the loocation of Abu Ghosh??</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5083,12 +5094,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh? Answer: Abu Ghosh is a small town in Israel, located 10 km west of Jerusalem. It is situated on the road between</t>
+          <t>What iis the loocation of Abu Ghosh?? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is a small town in Israel</t>
+          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5105,7 +5116,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -5118,7 +5129,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh?</t>
+          <t>What iis the loocation of Abu Ghosh??</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5131,12 +5142,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh? Answer: Abu Ghosh is a small town in Israel, located in the Jerusalem District, 10 km west of Jerusalem, on the</t>
+          <t>What iis the loocation of Abu Ghosh?? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is a small town in Israel</t>
+          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5153,7 +5164,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -5166,7 +5177,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh?</t>
+          <t>What iis the loocation of Abu Ghosh??</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5179,12 +5190,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh? Answer: Abu Ghosh is a small town in Israel, located 10 km west of Jerusalem. It is situated on the road between</t>
+          <t>What iis the loocation of Abu Ghosh?? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is a small town in Israel</t>
+          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5201,7 +5212,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -5214,7 +5225,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh?</t>
+          <t>What iis the loocation of Abu Ghosh??</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5227,12 +5238,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh? Answer: Abu Ghosh is a small town in Israel, located in the Jerusalem District, 10 km west of Jerusalem, on the</t>
+          <t>What iis the loocation of Abu Ghosh?? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is a small town in Israel</t>
+          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -5249,7 +5260,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5262,7 +5273,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh?</t>
+          <t>What iis the loocation of Abu Ghosh??</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5275,12 +5286,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>What is thee location of Abuu Ghoosh? Answer: Abu Ghosh is a small town in Israel, located 10 km west of Jerusalem. It is situated on the road between</t>
+          <t>What iis the loocation of Abu Ghosh?? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is a small town in Israel</t>
+          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -5297,7 +5308,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L101" t="n">
